--- a/data/ams_weekly_data/White_Mulberry/ads_report_week25.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week25.xlsx
@@ -479,7 +479,7 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -703,7 +703,7 @@
         <v>9</v>
       </c>
       <c r="F10" t="n">
-        <v>1414</v>
+        <v>1410</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>8</v>
       </c>
       <c r="F12" t="n">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
         <v>12</v>
       </c>
       <c r="F13" t="n">
-        <v>2592</v>
+        <v>2591</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -843,7 +843,7 @@
         <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -899,7 +899,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -927,7 +927,7 @@
         <v>21</v>
       </c>
       <c r="F18" t="n">
-        <v>3097</v>
+        <v>3091</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1151,7 +1151,7 @@
         <v>11</v>
       </c>
       <c r="F26" t="n">
-        <v>1138</v>
+        <v>1115</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
         <v>47</v>
       </c>
       <c r="F32" t="n">
-        <v>7095</v>
+        <v>7064</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1375,7 +1375,7 @@
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>11</v>
       </c>
       <c r="F35" t="n">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1711,7 +1711,7 @@
         <v>13</v>
       </c>
       <c r="F46" t="n">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1739,7 +1739,7 @@
         <v>5</v>
       </c>
       <c r="F47" t="n">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1907,7 +1907,7 @@
         <v>18</v>
       </c>
       <c r="F53" t="n">
-        <v>2719</v>
+        <v>2718</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1963,7 +1963,7 @@
         <v>11</v>
       </c>
       <c r="F55" t="n">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -2159,7 +2159,7 @@
         <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2187,7 +2187,7 @@
         <v>9</v>
       </c>
       <c r="F63" t="n">
-        <v>3347</v>
+        <v>3343</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2719,7 +2719,7 @@
         <v>13</v>
       </c>
       <c r="F82" t="n">
-        <v>2051</v>
+        <v>2033</v>
       </c>
       <c r="G82" t="n">
         <v>490.68</v>
@@ -2859,7 +2859,7 @@
         <v>17</v>
       </c>
       <c r="F87" t="n">
-        <v>976</v>
+        <v>969</v>
       </c>
       <c r="G87" t="n">
         <v>981.36</v>
@@ -2943,7 +2943,7 @@
         <v>1</v>
       </c>
       <c r="F90" t="n">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2971,7 +2971,7 @@
         <v>7</v>
       </c>
       <c r="F91" t="n">
-        <v>4639</v>
+        <v>4630</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -3187,7 +3187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3241,22 +3241,22 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1263</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>102.15</v>
+        <v>6.13</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -3274,22 +3274,22 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1456</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>452.03</v>
+        <v>6.13</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -3307,22 +3307,22 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-B0DB5VG39T - CT</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5028</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>452.8</v>
+        <v>6.13</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -3340,22 +3340,22 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5933333333333334</v>
+        <v>6.13</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -3373,22 +3373,22 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5933333333333334</v>
+        <v>6.13</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -3406,22 +3406,22 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5933333333333334</v>
+        <v>6.13</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -3439,25 +3439,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>728</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5933333333333334</v>
+        <v>74.86499999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>3643.645</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -3472,25 +3472,25 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>728</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5933333333333334</v>
+        <v>74.86499999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>3643.645</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -3505,25 +3505,25 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>484</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5933333333333334</v>
+        <v>62.59333333333333</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2429.096666666667</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -3538,25 +3538,25 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2221</v>
+        <v>484</v>
       </c>
       <c r="E11" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F11" t="n">
-        <v>406.93</v>
+        <v>62.59333333333333</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2429.096666666667</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -3571,25 +3571,25 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1590</v>
+        <v>484</v>
       </c>
       <c r="E12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F12" t="n">
-        <v>136.61</v>
+        <v>62.59333333333333</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2429.096666666667</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -3604,30 +3604,426 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
+          <t>SB-Lshape-Multi Asin- KT- phrase</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>B0BFVMDJ2K</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2168</v>
+      </c>
+      <c r="E13" t="n">
+        <v>52</v>
+      </c>
+      <c r="F13" t="n">
+        <v>301.88</v>
+      </c>
+      <c r="G13" t="n">
+        <v>7075.42</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1262</v>
+      </c>
+      <c r="E14" t="n">
+        <v>11</v>
+      </c>
+      <c r="F14" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>B0DP2WC5VW</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1456</v>
+      </c>
+      <c r="E15" t="n">
+        <v>22</v>
+      </c>
+      <c r="F15" t="n">
+        <v>452.03</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-B0DB5VG39T - CT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>5028</v>
+      </c>
+      <c r="E16" t="n">
+        <v>49</v>
+      </c>
+      <c r="F16" t="n">
+        <v>452.8</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.5933333333333334</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>B0DB5VVPSB</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.5933333333333334</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.5933333333333334</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>B0DB5YTQZV</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.5933333333333334</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.5933333333333334</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.5933333333333334</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2221</v>
+      </c>
+      <c r="E23" t="n">
+        <v>21</v>
+      </c>
+      <c r="F23" t="n">
+        <v>406.93</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1586</v>
+      </c>
+      <c r="E24" t="n">
+        <v>15</v>
+      </c>
+      <c r="F24" t="n">
+        <v>136.61</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>White Mulberry Monitor Arm-B0DB5VG39T-PT-KT-SBV</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>B0DB5VG39T</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D25" t="n">
         <v>1750</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E25" t="n">
         <v>24</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F25" t="n">
         <v>307.42</v>
       </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr">
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week25.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week25.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,22 +464,22 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Camb-B0BFW59TRG-L-Shape-Phrase-Exact-SP</t>
+          <t>Camb- Gaming Desk-B0CPFS24ML-CT-SP</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>175.28</v>
+        <v>202.98</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F2" t="n">
-        <v>1204</v>
+        <v>3146</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -492,22 +492,22 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Camb-B0CPT3Q25C - Motorized-SP-PT</t>
+          <t>Camb- Gaming Desk-B0CPFS24ML-Phrase-SP</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>675.08</v>
+        <v>101.74</v>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>1461</v>
+        <v>522</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -520,22 +520,22 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Camb-B0CPT3Q25C - Motorized-SP-PT</t>
+          <t>Camb- Motorized-SP-PT002</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>45.69</v>
+        <v>919.0400000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="F4" t="n">
-        <v>447</v>
+        <v>8029</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -548,22 +548,22 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Camb-Lshape-SP-KT-Phrase</t>
+          <t>Camb- Motorized-SP-PT002</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>58.5</v>
+        <v>324.4</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="F5" t="n">
-        <v>931</v>
+        <v>7676</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -576,7 +576,7 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Camb-Lshape-SP-KT-Phrase</t>
+          <t>Camb-B0BFW59TRG-L-Shape-Phrase-Exact-SP</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>148.12</v>
+        <v>689.6799999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F6" t="n">
-        <v>377</v>
+        <v>7051</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -604,22 +604,22 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Camb-Lshape-SP-PT-Exact</t>
+          <t>Camb-B0CPT3Q25C - Motorized-SP-PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>165.85</v>
+        <v>1420.56</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F7" t="n">
-        <v>653</v>
+        <v>2962</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -632,19 +632,19 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Camb-Lshape-SP-PT-Exact</t>
+          <t>Camb-B0CPT3Q25C - Motorized-SP-PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>118.74</v>
+        <v>45.69</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>487</v>
@@ -660,22 +660,22 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Camb-Motorized desk- B0DQ4YWSMC - PT 02</t>
+          <t>Camb-Gaming Desk-B0CPFS24ML-BM-SP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>259.83</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F9" t="n">
-        <v>21</v>
+        <v>1591</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -688,50 +688,50 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Camb-Motorized desk-B0DQ4YWSMC - BM</t>
+          <t>Camb-L shape-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>107.05</v>
+        <v>929.76</v>
       </c>
       <c r="E10" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="F10" t="n">
-        <v>1410</v>
+        <v>11430</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>14150.84</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Camb-Motorized desk-B0DQ4YWSMC - Exact</t>
+          <t>Camb-L shape-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.89</v>
+        <v>970.54</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="F11" t="n">
-        <v>83</v>
+        <v>7254</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -744,22 +744,22 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Camb-Motorized desk-B0DQ4YWSMC- Phrase</t>
+          <t>Camb-Lshape-SP-PT-Exact</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>92.34999999999999</v>
+        <v>274.68</v>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F12" t="n">
-        <v>1406</v>
+        <v>1285</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -772,22 +772,22 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Camb-Motorized sit stand-B0DQ4YWSMC- PT</t>
+          <t>Camb-Lshape-SP-PT-Exact</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>135.89</v>
+        <v>326.71</v>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F13" t="n">
-        <v>2591</v>
+        <v>1386</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -800,7 +800,7 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Camb-Motorized-SP-KT-BM</t>
+          <t>Camb-Motorized desk- B0DQ4YWSMC - PT 02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>542.65</v>
+        <v>70.33</v>
       </c>
       <c r="E14" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>6621</v>
+        <v>1460</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -828,22 +828,22 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Camb-SP- L Shaped-B0BFWD6SNF- Phrase</t>
+          <t>Camb-Motorized desk- SP- Defensive</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.82</v>
+        <v>115.29</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F15" t="n">
-        <v>642</v>
+        <v>1037</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -856,50 +856,50 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Camb-SP- L Shaped-B0BFWD6SNF-BM</t>
+          <t>Camb-Motorized desk- SP- Defensive</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>184.46</v>
+        <v>209.7</v>
       </c>
       <c r="E16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F16" t="n">
-        <v>2041</v>
+        <v>1949</v>
       </c>
       <c r="G16" t="n">
-        <v>7456.78</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Camb-SP- L Shaped-B0BFWD6SNF-Exact</t>
+          <t>Camb-Motorized desk-B0DQ4YWSMC - BM</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>742.79</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="F17" t="n">
-        <v>774</v>
+        <v>6093</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -912,22 +912,22 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Camb-SP- L Shaped-B0BFWD6SNF-PT</t>
+          <t>Camb-Motorized desk-B0DQ4YWSMC - Exact</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>212.96</v>
+        <v>28.04</v>
       </c>
       <c r="E18" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>3091</v>
+        <v>732</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -940,22 +940,22 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Camb-SP-Branded</t>
+          <t>Camb-Motorized desk-B0DQ4YWSMC- Phrase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>109.83</v>
+        <v>319.61</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="F19" t="n">
-        <v>1280</v>
+        <v>10406</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -968,50 +968,50 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Camb-SP-Branded</t>
+          <t>Camb-Motorized sit stand-B0DQ4YWSMC- PT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>468.49</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F20" t="n">
-        <v>525</v>
+        <v>9513</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>25425.43</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Camb-SP-Branded</t>
+          <t>Camb-Motorized-SP-KT-BM</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>24.06</v>
+        <v>3942.72</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>162</v>
       </c>
       <c r="F21" t="n">
-        <v>209</v>
+        <v>45928</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1024,7 +1024,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Camb-SP-Branded</t>
+          <t>Camb-SP- L Shape-B0BFWD6SNF- Phrase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1033,16 +1033,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>23.56</v>
+        <v>233.15</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F22" t="n">
-        <v>373</v>
+        <v>7568</v>
       </c>
       <c r="G22" t="n">
-        <v>7287.29</v>
+        <v>7075.42</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
@@ -1052,50 +1052,50 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Camb-SP-Branded</t>
+          <t>Camb-SP- L Shape-B0BFWD6SNF-BM</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>138.66</v>
+        <v>2034.58</v>
       </c>
       <c r="E23" t="n">
-        <v>6</v>
+        <v>113</v>
       </c>
       <c r="F23" t="n">
-        <v>1142</v>
+        <v>15194</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>21988.98</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Camb-SP-Branded</t>
+          <t>Camb-SP- L Shape-B0BFWD6SNF-Exact</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>26.96</v>
+        <v>251.45</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="F24" t="n">
-        <v>206</v>
+        <v>15149</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1108,50 +1108,50 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-B0BFVMDJ2K/B0BFWD6SNF- Exact/Phrase</t>
+          <t>Camb-SP- L Shape-B0BFWD6SNF-PT</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>453.87</v>
+        <v>1179.13</v>
       </c>
       <c r="E25" t="n">
-        <v>16</v>
+        <v>109</v>
       </c>
       <c r="F25" t="n">
-        <v>1759</v>
+        <v>11719</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>21988.98</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-B0BFWD6SNF - Broad</t>
+          <t>Camb-SP- L Shape-Multi Asin- Phrase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>90.23</v>
+        <v>20.02</v>
       </c>
       <c r="E26" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>1115</v>
+        <v>372</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1164,22 +1164,22 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-CDesk-Multiple Asin- PT</t>
+          <t>Camb-SP- L Shape-Multi Asin- Phrase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>28.08</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F27" t="n">
-        <v>138</v>
+        <v>742</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1192,7 +1192,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact 01</t>
+          <t>Camb-SP-Branded</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1201,13 +1201,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>425.96</v>
+        <v>266.28</v>
       </c>
       <c r="E28" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F28" t="n">
-        <v>8152</v>
+        <v>2686</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1220,22 +1220,22 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
+          <t>Camb-SP-Branded</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>275.68</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F29" t="n">
-        <v>663</v>
+        <v>2908</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
+          <t>Camb-SP-Branded</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1257,13 +1257,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>349.24</v>
+        <v>158.13</v>
       </c>
       <c r="E30" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F30" t="n">
-        <v>5721</v>
+        <v>909</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1276,7 +1276,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
+          <t>Camb-SP-Branded</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1285,26 +1285,26 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>56.7</v>
+        <v>82.62</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F31" t="n">
-        <v>989</v>
+        <v>1017</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>7287.29</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- BM</t>
+          <t>Camb-SP-Branded</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1313,13 +1313,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>630.1900000000001</v>
+        <v>447.19</v>
       </c>
       <c r="E32" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="F32" t="n">
-        <v>7064</v>
+        <v>4328</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1332,50 +1332,50 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- Exact</t>
+          <t>Camb-SP-Branded</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>460.99</v>
+        <v>114.21</v>
       </c>
       <c r="E33" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F33" t="n">
-        <v>3879</v>
+        <v>1181</v>
       </c>
       <c r="G33" t="n">
-        <v>12712.71</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- Exact - 01</t>
+          <t>Camb-SP-L shape-B0BFVMDJ2K/B0BFWD6SNF- Exact/Phrase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.12</v>
+        <v>2584.13</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="F34" t="n">
-        <v>826</v>
+        <v>17463</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1388,50 +1388,50 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk- B0CPT3Q25C-PT</t>
+          <t>Camb-SP-L shape-B0BFWD6SNF - Broad</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>146.48</v>
+        <v>938.6600000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="F35" t="n">
-        <v>1173</v>
+        <v>8669</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>28683.04</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk-B0CPT3Q25C - PT01</t>
+          <t>Camb-SP-L shape-CDesk-Multiple Asin- PT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>545.4400000000001</v>
+        <v>108.8</v>
       </c>
       <c r="E36" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F36" t="n">
-        <v>452</v>
+        <v>615</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1444,22 +1444,22 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- CT ref</t>
+          <t>Camb-SP-L shape-CDesk-Multiple Asin- PT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>370.85</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>1535</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1472,22 +1472,22 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- PT</t>
+          <t>Camb-SP-L shape-Multiple Asins- Exact/Phrase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>132.04</v>
+        <v>564.74</v>
       </c>
       <c r="E38" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="F38" t="n">
-        <v>1424</v>
+        <v>6889</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1500,50 +1500,50 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- Phrase</t>
+          <t>Camb-SP-L shape-Multiple Asins- Exact/Phrase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>271.32</v>
+        <v>2424.45</v>
       </c>
       <c r="E39" t="n">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="F39" t="n">
-        <v>2917</v>
+        <v>26777</v>
       </c>
       <c r="G39" t="n">
-        <v>7287.29</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML-PT01</t>
+          <t>Camb-SP-L shape-Multiple Asins- Exact/Phrase</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>127.83</v>
+        <v>277.22</v>
       </c>
       <c r="E40" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F40" t="n">
-        <v>749</v>
+        <v>4248</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1556,22 +1556,22 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Camb-SP-stand desk- B0DQ1NV8D2- PT</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact 01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>717.79</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F41" t="n">
-        <v>24</v>
+        <v>12031</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1584,106 +1584,106 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Camb-Zshape-Gaming- B0CPFS24ML-Phrase/Exact</t>
+          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- BM</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>551.12</v>
+        <v>2080.53</v>
       </c>
       <c r="E42" t="n">
-        <v>41</v>
+        <v>153</v>
       </c>
       <c r="F42" t="n">
-        <v>7304</v>
+        <v>25061</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>7287.29</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SP CT PT_B0CPFS24ML_Gaming</t>
+          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- Exact</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>309.76</v>
+        <v>4238.27</v>
       </c>
       <c r="E43" t="n">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="F43" t="n">
-        <v>1371</v>
+        <v>48342</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>25425.42</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SP_KT_L shape Non Performing Ex</t>
+          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- Exact - 01</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.73</v>
+        <v>282.12</v>
       </c>
       <c r="E44" t="n">
+        <v>21</v>
+      </c>
+      <c r="F44" t="n">
+        <v>5921</v>
+      </c>
+      <c r="G44" t="n">
+        <v>12712.71</v>
+      </c>
+      <c r="H44" t="n">
         <v>1</v>
-      </c>
-      <c r="F44" t="n">
-        <v>730</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SP_KT_L shape Non Performing Ex</t>
+          <t>Camb-SP-Motorized Desk- B0CPT3Q25C-PT</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>60.96</v>
+        <v>549.24</v>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="F45" t="n">
-        <v>38</v>
+        <v>6955</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1696,22 +1696,22 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SP_PT_L shape Non Performing PT</t>
+          <t>Camb-SP-Motorized Desk-B0CPT3Q25C - PT001</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>200.91</v>
+        <v>733.88</v>
       </c>
       <c r="E46" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="F46" t="n">
-        <v>1933</v>
+        <v>6171</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1724,22 +1724,22 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SP_PT_L shape Non Performing PT</t>
+          <t>Camb-SP-Motorized Desk-B0CPT3Q25C - PT001</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>78.73</v>
+        <v>394.3</v>
       </c>
       <c r="E47" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="F47" t="n">
-        <v>1267</v>
+        <v>8292</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1752,22 +1752,22 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5VG39T - PT</t>
+          <t>Camb-SP-Motorized Desk-B0CPT3Q25C - PT01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>1645.91</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>3037</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1780,78 +1780,78 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>WB- SP- B0DP32F346 - PT</t>
+          <t>Camb-SP-Motorized Desk-B0CPT3Q25C- Exact</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>372.42</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>484</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>2626.27</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>WM- Height Adj stand Dual-B0DB5YTQZV-SP-KT-Phrase/BM</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- CT ref</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>154.29</v>
+        <v>3573.42</v>
       </c>
       <c r="E50" t="n">
-        <v>7</v>
+        <v>177</v>
       </c>
       <c r="F50" t="n">
-        <v>889</v>
+        <v>15589</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>29149.16</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>WM- Height Adjustable stand- Dual-B0DB5YTQZV- PT</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- PT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>372.13</v>
+        <v>1455.33</v>
       </c>
       <c r="E51" t="n">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="F51" t="n">
-        <v>556</v>
+        <v>13693</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1864,78 +1864,78 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- Phrase</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>1992.7</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>16057</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>29149.14</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WM- SP- Height Adjustable stand- Dual-B0DB5YTQZV- Broad</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML-PT01</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>225.92</v>
+        <v>592.46</v>
       </c>
       <c r="E53" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="F53" t="n">
-        <v>2718</v>
+        <v>4172</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>21861.87</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WM- SP- Wall Mounted Stand- B0DP2WC5VW- Broad</t>
+          <t>Camb-SP-stand desk- B0DQ1NV8D2- PT</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>326.25</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>1158</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1948,50 +1948,50 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WM- SP- Wooden Arm- B0DP32F346- PT</t>
+          <t>Camb-Zshape-Gaming- B0CPFS24ML-Phrase/Exact</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>331.99</v>
+        <v>3410.2</v>
       </c>
       <c r="E55" t="n">
-        <v>11</v>
+        <v>231</v>
       </c>
       <c r="F55" t="n">
-        <v>2151</v>
+        <v>34316</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>7456.78</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>WM- SP-Wall Mounted Stand- B0DP2WC5VW- Exact &amp; Phrase</t>
+          <t>SP CT PT_B0CPFS24ML_Gaming</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>2196.54</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>16853</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2004,22 +2004,22 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WM- Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>SP_KT_L shape Non Performing Ex</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>12.73</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>1225</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2032,22 +2032,22 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>WM-Gas Spring MA- B0DB5VG39T-SP-KT-Phrase/BM</t>
+          <t>SP_KT_L shape Non Performing Ex</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>423.11</v>
+        <v>91.53</v>
       </c>
       <c r="E58" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F58" t="n">
-        <v>1322</v>
+        <v>1276</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2060,22 +2060,22 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>SP_PT_L shape Non Performing PT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>165.03</v>
+        <v>959.24</v>
       </c>
       <c r="E59" t="n">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="F59" t="n">
-        <v>1074</v>
+        <v>7743</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2088,22 +2088,22 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>SP_PT_L shape Non Performing PT</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>499.11</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>2895</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2116,22 +2116,22 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WB- SP- B0DB5VG39T - PT</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>107.3</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>1960</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2144,35 +2144,35 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
+          <t>WB- SP- B0DP2VVRND - PT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>B0DP3194QN</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>24.03</v>
+        <v>40.68</v>
       </c>
       <c r="E62" t="n">
+        <v>5</v>
+      </c>
+      <c r="F62" t="n">
+        <v>279</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1694.07</v>
+      </c>
+      <c r="H62" t="n">
         <v>1</v>
-      </c>
-      <c r="F62" t="n">
-        <v>1175</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
+          <t>WB- SP- B0DP32F346 - PT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2181,69 +2181,69 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>178.28</v>
+        <v>1544.5</v>
       </c>
       <c r="E63" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="F63" t="n">
-        <v>3343</v>
+        <v>2060</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>5252.54</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
+          <t>WM- Height Adj stand - B0DP2VVRND-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>346.65</v>
+        <v>2145.49</v>
       </c>
       <c r="E64" t="n">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="F64" t="n">
-        <v>5671</v>
+        <v>24607</v>
       </c>
       <c r="G64" t="n">
-        <v>2329.66</v>
+        <v>6776.25</v>
       </c>
       <c r="H64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Broad</t>
+          <t>WM- Height Adj stand Dual-B0DB5YTQZV-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>303.58</v>
+        <v>1162.35</v>
       </c>
       <c r="E65" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="F65" t="n">
-        <v>2334</v>
+        <v>7640</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2256,40 +2256,40 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
+          <t>WM- Height Adjustable stand- Dual-B0DB5YTQZV- PT</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>373.38</v>
+        <v>2987.19</v>
       </c>
       <c r="E66" t="n">
-        <v>11</v>
+        <v>94</v>
       </c>
       <c r="F66" t="n">
-        <v>725</v>
+        <v>6187</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>17249.16</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
+          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2299,7 +2299,7 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2312,50 +2312,50 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM- SP- Height Adjustable stand- Dual-B0DB5YTQZV- Broad</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>63.58</v>
+        <v>1086.52</v>
       </c>
       <c r="E68" t="n">
-        <v>5</v>
+        <v>78</v>
       </c>
       <c r="F68" t="n">
-        <v>370</v>
+        <v>13587</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>5082.2</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM- SP- Wall Mounted Stand- B0DP2WC5VW- Broad</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>17.28</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>519</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2368,22 +2368,22 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM- SP- Wooden Arm- B0DP32F346- PT</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>26.23</v>
+        <v>1505.07</v>
       </c>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="F70" t="n">
-        <v>364</v>
+        <v>6422</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2396,22 +2396,22 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM- SP-Wall Mounted Stand- B0DP2WC5VW- Exact &amp; Phrase</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.18</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2424,22 +2424,22 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM- Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>26.22</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>317</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-Gas Spring MA- B0DB5VG39T-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2461,41 +2461,41 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>14.54</v>
+        <v>2610.16</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="F73" t="n">
-        <v>150</v>
+        <v>8231</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>6988.98</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>38.1</v>
+        <v>701.15</v>
       </c>
       <c r="E74" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="F74" t="n">
-        <v>454</v>
+        <v>2988</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2508,22 +2508,22 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>26.8</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2536,40 +2536,40 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>113.92</v>
+        <v>528.25</v>
       </c>
       <c r="E76" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F76" t="n">
-        <v>730</v>
+        <v>4717</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>1694.07</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -2592,22 +2592,22 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>814.15</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F78" t="n">
-        <v>70</v>
+        <v>8248</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2620,22 +2620,22 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - PT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>363.38</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F79" t="n">
-        <v>2</v>
+        <v>2452</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2648,7 +2648,7 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - Phrase</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2657,13 +2657,13 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>163.8</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F80" t="n">
-        <v>8</v>
+        <v>653</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2676,78 +2676,78 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 -Phrase</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>750.8</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F81" t="n">
-        <v>15</v>
+        <v>10046</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>2626.27</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>212.68</v>
+        <v>640.8099999999999</v>
       </c>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="F82" t="n">
-        <v>2033</v>
+        <v>15177</v>
       </c>
       <c r="G82" t="n">
-        <v>490.68</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>B0FN4HDM6Z</t>
+          <t>B0DP3194QN</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>108.5</v>
+        <v>97.84</v>
       </c>
       <c r="E83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F83" t="n">
-        <v>1127</v>
+        <v>5730</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2760,134 +2760,134 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>B0FHVWHQHR</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>43.33</v>
+        <v>1326.06</v>
       </c>
       <c r="E84" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="F84" t="n">
-        <v>838</v>
+        <v>15693</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>6269.49</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>109.22</v>
+        <v>1914.52</v>
       </c>
       <c r="E85" t="n">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="F85" t="n">
-        <v>4665</v>
+        <v>20843</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>11540.3</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Broad</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>B0FHVWHQHR</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>2487.28</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="F86" t="n">
-        <v>129</v>
+        <v>25816</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>11648.3</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>436.44</v>
+        <v>1760.37</v>
       </c>
       <c r="E87" t="n">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="F87" t="n">
-        <v>969</v>
+        <v>7546</v>
       </c>
       <c r="G87" t="n">
-        <v>981.36</v>
+        <v>3643.22</v>
       </c>
       <c r="H87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>B0FN4HDM6Z</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>28.86</v>
+        <v>322.8</v>
       </c>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F88" t="n">
-        <v>47</v>
+        <v>1227</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2900,22 +2900,22 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>B0FHVWHQHR</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>170.7</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F89" t="n">
-        <v>79</v>
+        <v>490</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2928,22 +2928,22 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>7.82</v>
+        <v>26.66</v>
       </c>
       <c r="E90" t="n">
         <v>1</v>
       </c>
       <c r="F90" t="n">
-        <v>155</v>
+        <v>625</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2956,56 +2956,1120 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>White Mulberry Monitor Arm-B0DB5W4TCP-SP-Phrase</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>96.92</v>
+        <v>157.8</v>
       </c>
       <c r="E91" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F91" t="n">
-        <v>4630</v>
+        <v>2308</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>5294.91</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
+          <t>WM-SP-Monitor Arms- Branded</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>B0DB5VVPSB</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>192.84</v>
+      </c>
+      <c r="E92" t="n">
+        <v>9</v>
+      </c>
+      <c r="F92" t="n">
+        <v>2361</v>
+      </c>
+      <c r="G92" t="n">
+        <v>3861.86</v>
+      </c>
+      <c r="H92" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Arms- Branded</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>111.72</v>
+      </c>
+      <c r="E93" t="n">
+        <v>5</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1486</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Arms- Branded</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>B0DB5YTQZV</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>61.68</v>
+      </c>
+      <c r="E94" t="n">
+        <v>3</v>
+      </c>
+      <c r="F94" t="n">
+        <v>385</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Arms- Branded</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>88.55</v>
+      </c>
+      <c r="E95" t="n">
+        <v>4</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1061</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Arms- Branded</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>97.62</v>
+      </c>
+      <c r="E96" t="n">
+        <v>4</v>
+      </c>
+      <c r="F96" t="n">
+        <v>2099</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Arms- Defensive</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>129.39</v>
+      </c>
+      <c r="E97" t="n">
+        <v>10</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1841</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Arms- Defensive</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>B0DB5VVPSB</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>301.87</v>
+      </c>
+      <c r="E98" t="n">
+        <v>25</v>
+      </c>
+      <c r="F98" t="n">
+        <v>2587</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Arms- Defensive</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>115.49</v>
+      </c>
+      <c r="E99" t="n">
+        <v>9</v>
+      </c>
+      <c r="F99" t="n">
+        <v>778</v>
+      </c>
+      <c r="G99" t="n">
+        <v>1694.06</v>
+      </c>
+      <c r="H99" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Arms- Defensive</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>B0DB5YTQZV</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>421.46</v>
+      </c>
+      <c r="E100" t="n">
+        <v>32</v>
+      </c>
+      <c r="F100" t="n">
+        <v>3002</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Arms- Defensive</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>103.98</v>
+      </c>
+      <c r="E101" t="n">
+        <v>9</v>
+      </c>
+      <c r="F101" t="n">
+        <v>955</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Arms- Defensive</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>36.53</v>
+      </c>
+      <c r="E102" t="n">
+        <v>3</v>
+      </c>
+      <c r="F102" t="n">
+        <v>666</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - PT</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>B0DP2VVRND</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>211.17</v>
+      </c>
+      <c r="E103" t="n">
+        <v>24</v>
+      </c>
+      <c r="F103" t="n">
+        <v>903</v>
+      </c>
+      <c r="G103" t="n">
+        <v>1694.07</v>
+      </c>
+      <c r="H103" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - PT</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>225.3</v>
+      </c>
+      <c r="E104" t="n">
+        <v>17</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1061</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - Phrase</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>B0DP2VVRND</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>1120.71</v>
+      </c>
+      <c r="E105" t="n">
+        <v>64</v>
+      </c>
+      <c r="F105" t="n">
+        <v>3225</v>
+      </c>
+      <c r="G105" t="n">
+        <v>3388.14</v>
+      </c>
+      <c r="H105" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - Phrase</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>491.25</v>
+      </c>
+      <c r="E106" t="n">
+        <v>22</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1437</v>
+      </c>
+      <c r="G106" t="n">
+        <v>2372.03</v>
+      </c>
+      <c r="H106" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 -Phrase</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>B0DP2VVRND</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>825.1899999999999</v>
+      </c>
+      <c r="E107" t="n">
+        <v>35</v>
+      </c>
+      <c r="F107" t="n">
+        <v>4157</v>
+      </c>
+      <c r="G107" t="n">
+        <v>3388.14</v>
+      </c>
+      <c r="H107" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 -Phrase</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>411.05</v>
+      </c>
+      <c r="E108" t="n">
+        <v>19</v>
+      </c>
+      <c r="F108" t="n">
+        <v>3126</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>B0FN4DSQ6P</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>1364.54</v>
+      </c>
+      <c r="E109" t="n">
+        <v>82</v>
+      </c>
+      <c r="F109" t="n">
+        <v>13639</v>
+      </c>
+      <c r="G109" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="H109" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>B0FN4HDM6Z</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>207.66</v>
+      </c>
+      <c r="E110" t="n">
+        <v>12</v>
+      </c>
+      <c r="F110" t="n">
+        <v>2271</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>B0FHVWHQHR</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>153.32</v>
+      </c>
+      <c r="E111" t="n">
+        <v>12</v>
+      </c>
+      <c r="F111" t="n">
+        <v>7888</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>B0FN4D3C89</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>B0FN4DSQ6P</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>1139.61</v>
+      </c>
+      <c r="E113" t="n">
+        <v>92</v>
+      </c>
+      <c r="F113" t="n">
+        <v>27593</v>
+      </c>
+      <c r="G113" t="n">
+        <v>1472.04</v>
+      </c>
+      <c r="H113" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>B0FHVWHQHR</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>167.8</v>
+      </c>
+      <c r="E114" t="n">
+        <v>6</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1230</v>
+      </c>
+      <c r="G114" t="n">
+        <v>490.68</v>
+      </c>
+      <c r="H114" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>B0FN4DSQ6P</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>1640.24</v>
+      </c>
+      <c r="E115" t="n">
+        <v>63</v>
+      </c>
+      <c r="F115" t="n">
+        <v>5251</v>
+      </c>
+      <c r="G115" t="n">
+        <v>2216.96</v>
+      </c>
+      <c r="H115" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>B0FN4HDM6Z</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>417.38</v>
+      </c>
+      <c r="E116" t="n">
+        <v>13</v>
+      </c>
+      <c r="F116" t="n">
+        <v>752</v>
+      </c>
+      <c r="G116" t="n">
+        <v>3557.62</v>
+      </c>
+      <c r="H116" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>B0FHVWHQHR</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" t="n">
+        <v>359</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>B0FN4DSQ6P</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>51.29000000000001</v>
+      </c>
+      <c r="E118" t="n">
+        <v>5</v>
+      </c>
+      <c r="F118" t="n">
+        <v>897</v>
+      </c>
+      <c r="G118" t="n">
+        <v>490.68</v>
+      </c>
+      <c r="H118" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-BM-SP</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>279.49</v>
+      </c>
+      <c r="E119" t="n">
+        <v>21</v>
+      </c>
+      <c r="F119" t="n">
+        <v>4093</v>
+      </c>
+      <c r="G119" t="n">
+        <v>4659.32</v>
+      </c>
+      <c r="H119" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SP</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>57.97</v>
+      </c>
+      <c r="E120" t="n">
+        <v>5</v>
+      </c>
+      <c r="F120" t="n">
+        <v>634</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-Defense-SP</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>B0DP2VVRND</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" t="n">
+        <v>7</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-Defense-SP</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>B0DP3194QN</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" t="n">
+        <v>15</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-B0DB5W4TCP-SP-Phrase</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>680.8200000000001</v>
+      </c>
+      <c r="E123" t="n">
+        <v>47</v>
+      </c>
+      <c r="F123" t="n">
+        <v>24341</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-B0DP32F346-BM-SP</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>280.76</v>
+      </c>
+      <c r="E124" t="n">
+        <v>18</v>
+      </c>
+      <c r="F124" t="n">
+        <v>7762</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-B0DP32F346-PT-SP</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="n">
+        <v>6</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-B0DP32F346-Phrase-SP</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1</v>
+      </c>
+      <c r="F126" t="n">
+        <v>609</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-MultiAsin-Defense-SP</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" t="n">
+        <v>2</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-MultiAsin-Defense-SP</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>B0DP2VVRND</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" t="n">
+        <v>11</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-MultiAsin-Defense-SP</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>B0DP3194QN</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
           <t>White Mulberry-Dual Monitor Arm-B0DB5VVPSB-PT-SP</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>B0DB5VVPSB</t>
         </is>
       </c>
-      <c r="D92" t="n">
-        <v>287.1</v>
-      </c>
-      <c r="E92" t="n">
-        <v>17</v>
-      </c>
-      <c r="F92" t="n">
-        <v>1870</v>
-      </c>
-      <c r="G92" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0</v>
+      <c r="D130" t="n">
+        <v>1387.8</v>
+      </c>
+      <c r="E130" t="n">
+        <v>73</v>
+      </c>
+      <c r="F130" t="n">
+        <v>6332</v>
+      </c>
+      <c r="G130" t="n">
+        <v>7286.44</v>
+      </c>
+      <c r="H130" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3019,7 +4083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3068,22 +4132,22 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WM_Monitor Arm_High Selling_SD_VRM_7,14,30</t>
+          <t>L-Shape - SD Views RMKTNG - Apr'26 a30650</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>103.01</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>2622</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -3096,22 +4160,22 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WM_Monitor Arm_High Selling_SD_VRM_7,14,30</t>
+          <t>L-Shape - SD Views RMKTNG - Apr'26 a30650</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>228.92</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>9199</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -3124,12 +4188,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WM_Monitor Arm_High Selling_SD_VRM_7,14,30</t>
+          <t>L-Shape - SD Views RMKTNG - Apr'26 a30650</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -3152,28 +4216,252 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
+          <t>L-Shape SD Purchase RMKTNG - Apr'26 f19c32</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>B0BFVMDJ2K</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>L-Shape SD Purchase RMKTNG - Apr'26 f19c32</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>B0BFVNS8HS</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>L-Shape SD Purchase RMKTNG - Apr'26 f19c32</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>B0BFW59TRG</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SD_VR_Z Shape Desk_BMC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>WM_Monitor Arm_High Selling_SD_VRM_7,14,30</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>426.13</v>
+      </c>
+      <c r="E9" t="n">
+        <v>48</v>
+      </c>
+      <c r="F9" t="n">
+        <v>17712</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4776.27</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>WM_Monitor Arm_High Selling_SD_VRM_7,14,30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1121.58</v>
+      </c>
+      <c r="E10" t="n">
+        <v>102</v>
+      </c>
+      <c r="F10" t="n">
+        <v>34083</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>WM_Monitor Arm_High Selling_SD_VRM_7,14,30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>B0DP2VVRND</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>390.91</v>
+      </c>
+      <c r="E11" t="n">
+        <v>39</v>
+      </c>
+      <c r="F11" t="n">
+        <v>16947</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1694.07</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>WM_Monitor Arm_High Selling_SD_VRM_7,14,30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>79.02000000000001</v>
+      </c>
+      <c r="E12" t="n">
+        <v>13</v>
+      </c>
+      <c r="F12" t="n">
+        <v>7874</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>WM_Monitor Arm_High Selling_SD_VRM_7,14,30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>B0DP32F346</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>215.57</v>
-      </c>
-      <c r="E5" t="n">
-        <v>39</v>
-      </c>
-      <c r="F5" t="n">
-        <v>9967</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
+      <c r="D13" t="n">
+        <v>1120.83</v>
+      </c>
+      <c r="E13" t="n">
+        <v>141</v>
+      </c>
+      <c r="F13" t="n">
+        <v>42161</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2626.27</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3187,7 +4475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3241,7 +4529,7 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>Camb Gaming Desk-B0CPFS24ML-BM-Product Collection-SB</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3250,13 +4538,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>6.13</v>
+        <v>6.916666666666667</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -3274,22 +4562,22 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>Camb Gaming Desk-B0CPFS24ML-BM-Product Collection-SB</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>6.13</v>
+        <v>6.916666666666667</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -3307,22 +4595,22 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>Camb Gaming Desk-B0CPFS24ML-BM-Product Collection-SB</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>6.13</v>
+        <v>6.916666666666667</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -3345,11 +4633,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -3378,11 +4666,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3411,11 +4699,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3439,25 +4727,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>728</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>74.86499999999999</v>
+        <v>6.13</v>
       </c>
       <c r="G8" t="n">
-        <v>3643.645</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -3472,25 +4760,25 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>728</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>74.86499999999999</v>
+        <v>6.13</v>
       </c>
       <c r="G9" t="n">
-        <v>3643.645</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -3505,25 +4793,25 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>484</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>62.59333333333333</v>
+        <v>6.13</v>
       </c>
       <c r="G10" t="n">
-        <v>2429.096666666667</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -3538,28 +4826,28 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>484</v>
+        <v>4946</v>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>168</v>
       </c>
       <c r="F11" t="n">
-        <v>62.59333333333333</v>
+        <v>524.655</v>
       </c>
       <c r="G11" t="n">
-        <v>2429.096666666667</v>
+        <v>18006.35</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -3571,28 +4859,28 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>484</v>
+        <v>4946</v>
       </c>
       <c r="E12" t="n">
-        <v>9</v>
+        <v>168</v>
       </c>
       <c r="F12" t="n">
-        <v>62.59333333333333</v>
+        <v>524.655</v>
       </c>
       <c r="G12" t="n">
-        <v>2429.096666666667</v>
+        <v>18006.35</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -3604,25 +4892,25 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SB-Lshape-Multi Asin- KT- phrase</t>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2168</v>
+        <v>2715</v>
       </c>
       <c r="E13" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F13" t="n">
-        <v>301.88</v>
+        <v>365.4366666666667</v>
       </c>
       <c r="G13" t="n">
-        <v>7075.42</v>
+        <v>6666.666666666667</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
@@ -3637,28 +4925,28 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1262</v>
+        <v>2715</v>
       </c>
       <c r="E14" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="F14" t="n">
-        <v>102.15</v>
+        <v>365.4366666666667</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>6666.666666666667</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3670,28 +4958,28 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1456</v>
+        <v>2715</v>
       </c>
       <c r="E15" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F15" t="n">
-        <v>452.03</v>
+        <v>365.4366666666667</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>6666.666666666667</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -3703,28 +4991,28 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-B0DB5VG39T - CT</t>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5028</v>
+        <v>3940</v>
       </c>
       <c r="E16" t="n">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="F16" t="n">
-        <v>452.8</v>
+        <v>516.4475</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>10613.13</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -3736,28 +5024,28 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>3940</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5933333333333334</v>
+        <v>516.4475</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>10613.13</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3769,28 +5057,28 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>3940</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5933333333333334</v>
+        <v>516.4475</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>10613.13</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3802,28 +5090,28 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>3940</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5933333333333334</v>
+        <v>516.4475</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>10613.13</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3835,28 +5123,28 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>8191</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5933333333333334</v>
+        <v>1126.53</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2626.27</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3868,22 +5156,22 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>9510</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5933333333333334</v>
+        <v>2359.25</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -3901,28 +5189,28 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>WM-SB-Monitor Arms-B0DB5VG39T - CT</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>17046</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5933333333333334</v>
+        <v>2214.98</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>5972.879999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3934,7 +5222,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+          <t>WM-SB-Monitor Arms-Branded</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3943,16 +5231,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2221</v>
+        <v>14</v>
       </c>
       <c r="E23" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>406.93</v>
+        <v>14.7</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>388.2766666666666</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -3967,25 +5255,25 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
+          <t>WM-SB-Monitor Arms-Branded</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1586</v>
+        <v>14</v>
       </c>
       <c r="E24" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>136.61</v>
+        <v>14.7</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>388.2766666666666</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -4000,30 +5288,261 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>14</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="G25" t="n">
+        <v>388.2766666666666</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>B0DB5YTQZV</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>14</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="G26" t="n">
+        <v>388.2766666666666</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>14</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="G27" t="n">
+        <v>388.2766666666666</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>14</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="G28" t="n">
+        <v>388.2766666666666</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>14454</v>
+      </c>
+      <c r="E29" t="n">
+        <v>128</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2631.87</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3643.22</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1427</v>
+      </c>
+      <c r="E30" t="n">
+        <v>9</v>
+      </c>
+      <c r="F30" t="n">
+        <v>90.74000000000001</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>9967</v>
+      </c>
+      <c r="E31" t="n">
+        <v>102</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1039.22</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4659.32</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>White Mulberry Monitor Arm-B0DB5VG39T-PT-KT-SBV</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>B0DB5VG39T</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>1750</v>
-      </c>
-      <c r="E25" t="n">
-        <v>24</v>
-      </c>
-      <c r="F25" t="n">
-        <v>307.42</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="inlineStr">
+      <c r="D32" t="n">
+        <v>14477</v>
+      </c>
+      <c r="E32" t="n">
+        <v>143</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1856.99</v>
+      </c>
+      <c r="G32" t="n">
+        <v>12241.52</v>
+      </c>
+      <c r="H32" t="n">
+        <v>5</v>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week25.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week25.xlsx
@@ -4475,7 +4475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4835,19 +4835,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4946</v>
+        <v>2437</v>
       </c>
       <c r="E11" t="n">
-        <v>168</v>
+        <v>83</v>
       </c>
       <c r="F11" t="n">
-        <v>524.655</v>
+        <v>258.4578935583513</v>
       </c>
       <c r="G11" t="n">
-        <v>18006.35</v>
+        <v>8870.368702622522</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -4864,23 +4864,23 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4946</v>
+        <v>2437</v>
       </c>
       <c r="E12" t="n">
-        <v>168</v>
+        <v>83</v>
       </c>
       <c r="F12" t="n">
-        <v>524.655</v>
+        <v>258.4578935583513</v>
       </c>
       <c r="G12" t="n">
-        <v>18006.35</v>
+        <v>8870.368702622522</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -4892,28 +4892,28 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2715</v>
+        <v>5019</v>
       </c>
       <c r="E13" t="n">
-        <v>44</v>
+        <v>171</v>
       </c>
       <c r="F13" t="n">
-        <v>365.4366666666667</v>
+        <v>532.3942128832973</v>
       </c>
       <c r="G13" t="n">
-        <v>6666.666666666667</v>
+        <v>18271.96259475495</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -4930,23 +4930,23 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2715</v>
+        <v>8146</v>
       </c>
       <c r="E14" t="n">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="F14" t="n">
-        <v>365.4366666666667</v>
+        <v>1096.31</v>
       </c>
       <c r="G14" t="n">
-        <v>6666.666666666667</v>
+        <v>20000</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -4958,28 +4958,28 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2715</v>
+        <v>12607</v>
       </c>
       <c r="E15" t="n">
-        <v>44</v>
+        <v>286</v>
       </c>
       <c r="F15" t="n">
-        <v>365.4366666666667</v>
+        <v>1652.632</v>
       </c>
       <c r="G15" t="n">
-        <v>6666.666666666667</v>
+        <v>33962.016</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -4996,23 +4996,23 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3940</v>
+        <v>3152</v>
       </c>
       <c r="E16" t="n">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="F16" t="n">
-        <v>516.4475</v>
+        <v>413.158</v>
       </c>
       <c r="G16" t="n">
-        <v>10613.13</v>
+        <v>8490.503999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -5024,28 +5024,28 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SB-L shape-Multi Asin- KT- phrase</t>
+          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3940</v>
+        <v>8191</v>
       </c>
       <c r="E17" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F17" t="n">
-        <v>516.4475</v>
+        <v>1126.53</v>
       </c>
       <c r="G17" t="n">
-        <v>10613.13</v>
+        <v>2626.27</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -5057,28 +5057,28 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SB-L shape-Multi Asin- KT- phrase</t>
+          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3940</v>
+        <v>9510</v>
       </c>
       <c r="E18" t="n">
-        <v>89</v>
+        <v>159</v>
       </c>
       <c r="F18" t="n">
-        <v>516.4475</v>
+        <v>2359.25</v>
       </c>
       <c r="G18" t="n">
-        <v>10613.13</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -5090,28 +5090,28 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SB-L shape-Multi Asin- KT- phrase</t>
+          <t>WM-SB-Monitor Arms-B0DB5VG39T - CT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3940</v>
+        <v>6649</v>
       </c>
       <c r="E19" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="F19" t="n">
-        <v>516.4475</v>
+        <v>863.9300148002304</v>
       </c>
       <c r="G19" t="n">
-        <v>10613.13</v>
+        <v>2329.66</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -5123,25 +5123,25 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
+          <t>WM-SB-Monitor Arms-B0DB5VG39T - CT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8191</v>
+        <v>10397</v>
       </c>
       <c r="E20" t="n">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="F20" t="n">
-        <v>1126.53</v>
+        <v>1351.04998519977</v>
       </c>
       <c r="G20" t="n">
-        <v>2626.27</v>
+        <v>3643.22</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
@@ -5156,28 +5156,28 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>WM-SB-Monitor Arms-Branded</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>9510</v>
+        <v>86</v>
       </c>
       <c r="E21" t="n">
-        <v>159</v>
+        <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>2359.25</v>
+        <v>88.2</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2329.66</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -5189,28 +5189,28 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-B0DB5VG39T - CT</t>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>17046</v>
+        <v>14454</v>
       </c>
       <c r="E22" t="n">
-        <v>192</v>
+        <v>128</v>
       </c>
       <c r="F22" t="n">
-        <v>2214.98</v>
+        <v>2631.87</v>
       </c>
       <c r="G22" t="n">
-        <v>5972.879999999999</v>
+        <v>3643.22</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -5222,25 +5222,25 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14</v>
+        <v>1427</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F23" t="n">
-        <v>14.7</v>
+        <v>90.74000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>388.2766666666666</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -5255,28 +5255,28 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14</v>
+        <v>9967</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="F24" t="n">
-        <v>14.7</v>
+        <v>1039.22</v>
       </c>
       <c r="G24" t="n">
-        <v>388.2766666666666</v>
+        <v>4659.32</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -5288,261 +5288,30 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-PT-KT-SBV</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14</v>
+        <v>14477</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>143</v>
       </c>
       <c r="F25" t="n">
-        <v>14.7</v>
+        <v>1856.99</v>
       </c>
       <c r="G25" t="n">
-        <v>388.2766666666666</v>
+        <v>12241.52</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I25" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>B0DB5YTQZV</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>14</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="G26" t="n">
-        <v>388.2766666666666</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>B0DP2Z5DQ9</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>14</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="G27" t="n">
-        <v>388.2766666666666</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>B0DP32F346</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>14</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="G28" t="n">
-        <v>388.2766666666666</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>14454</v>
-      </c>
-      <c r="E29" t="n">
-        <v>128</v>
-      </c>
-      <c r="F29" t="n">
-        <v>2631.87</v>
-      </c>
-      <c r="G29" t="n">
-        <v>3643.22</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>B0DP2Z5DQ9</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>1427</v>
-      </c>
-      <c r="E30" t="n">
-        <v>9</v>
-      </c>
-      <c r="F30" t="n">
-        <v>90.74000000000001</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>9967</v>
-      </c>
-      <c r="E31" t="n">
-        <v>102</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1039.22</v>
-      </c>
-      <c r="G31" t="n">
-        <v>4659.32</v>
-      </c>
-      <c r="H31" t="n">
-        <v>2</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>White Mulberry Monitor Arm-B0DB5VG39T-PT-KT-SBV</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>14477</v>
-      </c>
-      <c r="E32" t="n">
-        <v>143</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1856.99</v>
-      </c>
-      <c r="G32" t="n">
-        <v>12241.52</v>
-      </c>
-      <c r="H32" t="n">
-        <v>5</v>
-      </c>
-      <c r="I32" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week25.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week25.xlsx
@@ -1067,7 +1067,7 @@
         <v>113</v>
       </c>
       <c r="F23" t="n">
-        <v>15194</v>
+        <v>15193</v>
       </c>
       <c r="G23" t="n">
         <v>21988.98</v>
@@ -2187,7 +2187,7 @@
         <v>39</v>
       </c>
       <c r="F63" t="n">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="G63" t="n">
         <v>5252.54</v>
@@ -2218,10 +2218,10 @@
         <v>24607</v>
       </c>
       <c r="G64" t="n">
-        <v>6776.25</v>
+        <v>11716.09</v>
       </c>
       <c r="H64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
@@ -2327,7 +2327,7 @@
         <v>78</v>
       </c>
       <c r="F68" t="n">
-        <v>13587</v>
+        <v>13586</v>
       </c>
       <c r="G68" t="n">
         <v>5082.2</v>
@@ -2831,7 +2831,7 @@
         <v>143</v>
       </c>
       <c r="F86" t="n">
-        <v>25816</v>
+        <v>25814</v>
       </c>
       <c r="G86" t="n">
         <v>11648.3</v>
@@ -3223,7 +3223,7 @@
         <v>32</v>
       </c>
       <c r="F100" t="n">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3251,7 +3251,7 @@
         <v>9</v>
       </c>
       <c r="F101" t="n">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>5</v>
       </c>
       <c r="F120" t="n">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
         <v>47</v>
       </c>
       <c r="F123" t="n">
-        <v>24341</v>
+        <v>24337</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -4343,7 +4343,7 @@
         <v>48</v>
       </c>
       <c r="F9" t="n">
-        <v>17712</v>
+        <v>17707</v>
       </c>
       <c r="G9" t="n">
         <v>4776.27</v>
@@ -4371,7 +4371,7 @@
         <v>102</v>
       </c>
       <c r="F10" t="n">
-        <v>34083</v>
+        <v>34078</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -4455,7 +4455,7 @@
         <v>141</v>
       </c>
       <c r="F13" t="n">
-        <v>42161</v>
+        <v>42152</v>
       </c>
       <c r="G13" t="n">
         <v>2626.27</v>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week25.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week25.xlsx
@@ -1039,7 +1039,7 @@
         <v>20</v>
       </c>
       <c r="F22" t="n">
-        <v>7568</v>
+        <v>7566</v>
       </c>
       <c r="G22" t="n">
         <v>7075.42</v>
@@ -1067,7 +1067,7 @@
         <v>113</v>
       </c>
       <c r="F23" t="n">
-        <v>15193</v>
+        <v>15192</v>
       </c>
       <c r="G23" t="n">
         <v>21988.98</v>
@@ -1095,7 +1095,7 @@
         <v>23</v>
       </c>
       <c r="F24" t="n">
-        <v>15149</v>
+        <v>15147</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>79</v>
       </c>
       <c r="F35" t="n">
-        <v>8669</v>
+        <v>8668</v>
       </c>
       <c r="G35" t="n">
         <v>28683.04</v>
@@ -1627,7 +1627,7 @@
         <v>104</v>
       </c>
       <c r="F43" t="n">
-        <v>48342</v>
+        <v>48341</v>
       </c>
       <c r="G43" t="n">
         <v>25425.42</v>
@@ -1739,7 +1739,7 @@
         <v>27</v>
       </c>
       <c r="F47" t="n">
-        <v>8292</v>
+        <v>8290</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1966,10 +1966,10 @@
         <v>34316</v>
       </c>
       <c r="G55" t="n">
-        <v>7456.78</v>
+        <v>14744.07</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -1991,7 +1991,7 @@
         <v>222</v>
       </c>
       <c r="F56" t="n">
-        <v>16853</v>
+        <v>16851</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2554,10 +2554,10 @@
         <v>4717</v>
       </c>
       <c r="G76" t="n">
-        <v>1694.07</v>
+        <v>3430.51</v>
       </c>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -3397,7 +3397,7 @@
         <v>2372.03</v>
       </c>
       <c r="H106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -3895,7 +3895,7 @@
         <v>18</v>
       </c>
       <c r="F124" t="n">
-        <v>7762</v>
+        <v>7761</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>102</v>
       </c>
       <c r="F10" t="n">
-        <v>34078</v>
+        <v>34076</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -5108,10 +5108,10 @@
         <v>863.9300148002304</v>
       </c>
       <c r="G19" t="n">
-        <v>2329.66</v>
+        <v>1421.000238611859</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>1351.04998519977</v>
       </c>
       <c r="G20" t="n">
-        <v>3643.22</v>
+        <v>2222.219761388141</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
